--- a/data/sites/manufacturing/Quality Assurance/corrective-and-preventive-action-capa-log.xlsx
+++ b/data/sites/manufacturing/Quality Assurance/corrective-and-preventive-action-capa-log.xlsx
@@ -7,7 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Architecture" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Controls" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 KPIs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 RACI Matrix" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Procedures" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Risk Register" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Quality Audit" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Escalations" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 SLAs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Roadmap" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Sign-off" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,11 +38,15 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="14"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,13 +75,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -141,6 +157,186 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -432,19 +628,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Corrective and Preventive Action (CAPA) Log</t>
+          <t>Corrective and Preventive Action (CAPA) Log - Section 1: Executive Summary &amp; Scope</t>
         </is>
       </c>
     </row>
@@ -455,107 +651,2261 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="45" customHeight="1">
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Tracks open CAPAs from root cause through verification of effectiveness, with owner and due date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+          <t>Tracks open CAPAs from root cause through verification of effectiveness, with owner and due date. Section 1 (Executive Summary &amp; Scope) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Defines the operational charter, scope boundaries, and executive accountability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 1.1: Root cause analysis uses the 5-Why or fishbone method depending on complexity. Secondary control 1.2: Containment actions must be implemented within 48 hours of CAPA opening.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>CAPA ID</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Issue</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CAPA-114</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Seal leak on Line 2</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Carlos Ibarra</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Verification</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAPA-118</t>
+          <t>CAPA-114</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Label print smearing</t>
+          <t>Seal leak on Line 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Linda Park</t>
+          <t>Carlos Ibarra</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Verification</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>CAPA-118</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Label print smearing</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Linda Park</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>CAPA-121</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Torque spec drift Station 7</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Grace Liu</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>• Root cause analysis uses the 5-Why or fishbone method depending on complexity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Containment actions must be implemented within 48 hours of CAPA opening.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Section 1 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Corrective and Preventive Action (CAPA) Log - Section 10: Cross-Functional Dependencies</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks open CAPAs from root cause through verification of effectiveness, with owner and due date. Section 10 (Cross-Functional Dependencies) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Documents upstream and downstream team dependencies and service-level commitments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 10.1: Containment actions must be implemented within 48 hours of CAPA opening. Secondary control 10.2: Effectiveness checks are scheduled 30-60 days after corrective action implementation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>CAPA ID</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAPA-114</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Seal leak on Line 2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Carlos Ibarra</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAPA-118</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Label print smearing</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Linda Park</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAPA-121</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Torque spec drift Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Seal leak on Line 2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Carlos Ibarra</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 10 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Containment actions must be implemented within 48 hours of CAPA opening.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Effectiveness checks are scheduled 30-60 days after corrective action implementation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 10 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Corrective and Preventive Action (CAPA) Log - Section 11: Continuous Improvement Roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks open CAPAs from root cause through verification of effectiveness, with owner and due date. Section 11 (Continuous Improvement Roadmap) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Schedules quarterly optimization milestones, automation targets, and capability reviews.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 11.1: Effectiveness checks are scheduled 30-60 days after corrective action implementation. Secondary control 11.2: CAPAs older than 90 days without closure are escalated to the plant quality review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>CAPA ID</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAPA-114</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Seal leak on Line 2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Carlos Ibarra</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAPA-118</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Label print smearing</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Linda Park</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAPA-121</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Torque spec drift Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Label print smearing</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Linda Park</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 11 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Effectiveness checks are scheduled 30-60 days after corrective action implementation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• CAPAs older than 90 days without closure are escalated to the plant quality review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 11 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Corrective and Preventive Action (CAPA) Log - Section 12: Appendix, Lineage &amp; Sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks open CAPAs from root cause through verification of effectiveness, with owner and due date. Section 12 (Appendix, Lineage &amp; Sign-off) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Records document lineage, governance metadata, version history, and owner sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 12.1: CAPAs older than 90 days without closure are escalated to the plant quality review. Secondary control 12.2: Root cause analysis uses the 5-Why or fishbone method depending on complexity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>CAPA ID</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAPA-114</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Seal leak on Line 2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Carlos Ibarra</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAPA-118</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Label print smearing</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Linda Park</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAPA-121</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Torque spec drift Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Torque spec drift Station 7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 12 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• CAPAs older than 90 days without closure are escalated to the plant quality review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Root cause analysis uses the 5-Why or fishbone method depending on complexity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 12 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Corrective and Preventive Action (CAPA) Log - Section 2: Architecture &amp; Process Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks open CAPAs from root cause through verification of effectiveness, with owner and due date. Section 2 (Architecture &amp; Process Flow) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Maps end-to-end process stages, handoff gates, and system-of-record integrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 2.1: Containment actions must be implemented within 48 hours of CAPA opening. Secondary control 2.2: Effectiveness checks are scheduled 30-60 days after corrective action implementation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>CAPA ID</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAPA-114</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Seal leak on Line 2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Carlos Ibarra</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAPA-118</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Label print smearing</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Linda Park</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAPA-121</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Torque spec drift Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Label print smearing</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Linda Park</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 2 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Containment actions must be implemented within 48 hours of CAPA opening.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Effectiveness checks are scheduled 30-60 days after corrective action implementation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 2 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Corrective and Preventive Action (CAPA) Log - Section 3: Governance Standards &amp; Controls</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks open CAPAs from root cause through verification of effectiveness, with owner and due date. Section 3 (Governance Standards &amp; Controls) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Establishes mandatory compliance controls, approval thresholds, and audit evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 3.1: Effectiveness checks are scheduled 30-60 days after corrective action implementation. Secondary control 3.2: CAPAs older than 90 days without closure are escalated to the plant quality review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>CAPA ID</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAPA-114</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Seal leak on Line 2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Carlos Ibarra</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAPA-118</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Label print smearing</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Linda Park</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAPA-121</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Torque spec drift Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Torque spec drift Station 7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 3 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Effectiveness checks are scheduled 30-60 days after corrective action implementation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• CAPAs older than 90 days without closure are escalated to the plant quality review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 3 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Corrective and Preventive Action (CAPA) Log - Section 4: Operational KPIs &amp; Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks open CAPAs from root cause through verification of effectiveness, with owner and due date. Section 4 (Operational KPIs &amp; Benchmarks) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Tracks baseline performance, target SLAs, and quarterly benchmark progression.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 4.1: CAPAs older than 90 days without closure are escalated to the plant quality review. Secondary control 4.2: Root cause analysis uses the 5-Why or fishbone method depending on complexity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>CAPA ID</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAPA-114</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Seal leak on Line 2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Carlos Ibarra</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAPA-118</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Label print smearing</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Linda Park</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAPA-121</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Torque spec drift Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Seal leak on Line 2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Carlos Ibarra</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 4 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• CAPAs older than 90 days without closure are escalated to the plant quality review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Root cause analysis uses the 5-Why or fishbone method depending on complexity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 4 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Corrective and Preventive Action (CAPA) Log - Section 5: Roles, Responsibilities &amp; RACI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks open CAPAs from root cause through verification of effectiveness, with owner and due date. Section 5 (Roles, Responsibilities &amp; RACI) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Clarifies ownership across accountable executives, operational leads, and reviewers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 5.1: Root cause analysis uses the 5-Why or fishbone method depending on complexity. Secondary control 5.2: Containment actions must be implemented within 48 hours of CAPA opening.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>CAPA ID</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAPA-114</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Seal leak on Line 2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Carlos Ibarra</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAPA-118</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Label print smearing</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Linda Park</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAPA-121</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Torque spec drift Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Label print smearing</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Linda Park</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 5 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Root cause analysis uses the 5-Why or fishbone method depending on complexity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Containment actions must be implemented within 48 hours of CAPA opening.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 5 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Corrective and Preventive Action (CAPA) Log - Section 6: Standard Operating Procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks open CAPAs from root cause through verification of effectiveness, with owner and due date. Section 6 (Standard Operating Procedures) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Provides step-by-step execution checklists, intake criteria, and verification gates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 6.1: Containment actions must be implemented within 48 hours of CAPA opening. Secondary control 6.2: Effectiveness checks are scheduled 30-60 days after corrective action implementation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>CAPA ID</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAPA-114</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Seal leak on Line 2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Carlos Ibarra</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAPA-118</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Label print smearing</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Linda Park</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAPA-121</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Torque spec drift Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-6</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Torque spec drift Station 7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 6 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Containment actions must be implemented within 48 hours of CAPA opening.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Effectiveness checks are scheduled 30-60 days after corrective action implementation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 6 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Corrective and Preventive Action (CAPA) Log - Section 7: Risk Register &amp; Mitigations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks open CAPAs from root cause through verification of effectiveness, with owner and due date. Section 7 (Risk Register &amp; Mitigations) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Catalogs operational, compliance, and delivery risks alongside preventive mitigations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 7.1: Effectiveness checks are scheduled 30-60 days after corrective action implementation. Secondary control 7.2: CAPAs older than 90 days without closure are escalated to the plant quality review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>CAPA ID</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAPA-114</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Seal leak on Line 2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Carlos Ibarra</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAPA-118</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Label print smearing</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Linda Park</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAPA-121</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Torque spec drift Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-7</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Seal leak on Line 2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Carlos Ibarra</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 7 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Effectiveness checks are scheduled 30-60 days after corrective action implementation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• CAPAs older than 90 days without closure are escalated to the plant quality review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 7 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Corrective and Preventive Action (CAPA) Log - Section 8: Quality Assurance &amp; Audits</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks open CAPAs from root cause through verification of effectiveness, with owner and due date. Section 8 (Quality Assurance &amp; Audits) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Specifies sampling frequencies, inspection tolerances, and nonconformance workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 8.1: CAPAs older than 90 days without closure are escalated to the plant quality review. Secondary control 8.2: Root cause analysis uses the 5-Why or fishbone method depending on complexity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>CAPA ID</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAPA-114</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Seal leak on Line 2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Carlos Ibarra</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAPA-118</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Label print smearing</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Linda Park</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAPA-121</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Torque spec drift Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Label print smearing</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Linda Park</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 8 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• CAPAs older than 90 days without closure are escalated to the plant quality review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Root cause analysis uses the 5-Why or fishbone method depending on complexity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 8 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Corrective and Preventive Action (CAPA) Log - Section 9: Exception Handling &amp; Escalations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks open CAPAs from root cause through verification of effectiveness, with owner and due date. Section 9 (Exception Handling &amp; Escalations) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Outlines severity tiers, response SLAs, and cross-functional escalation paths.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 9.1: Root cause analysis uses the 5-Why or fishbone method depending on complexity. Secondary control 9.2: Containment actions must be implemented within 48 hours of CAPA opening.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>CAPA ID</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAPA-114</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Seal leak on Line 2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Carlos Ibarra</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAPA-118</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Label print smearing</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Linda Park</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAPA-121</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Torque spec drift Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Torque spec drift Station 7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 9 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Root cause analysis uses the 5-Why or fishbone method depending on complexity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Containment actions must be implemented within 48 hours of CAPA opening.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 9 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>